--- a/quizzes/020_food_delivery_agent_quiz_form--quizzes.xlsx
+++ b/quizzes/020_food_delivery_agent_quiz_form--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -742,8 +742,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -771,12 +771,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -822,12 +822,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'price'}</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Price'}</t>
+          <t>Price</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'speed_of_delivery'}</t>
+          <t>speed_of_delivery</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Speed of delivery'}</t>
+          <t>Speed of delivery</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'quality_of_food'}</t>
+          <t>quality_of_food</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Quality of food'}</t>
+          <t>Quality of food</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'several_times_a_week'}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Several times a week'}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
